--- a/workbooks/professor_outreach.xlsx
+++ b/workbooks/professor_outreach.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Outreach</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:57:19Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:57:19Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
